--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_684_Saudi_Arabia_Persian_Gulf.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_684_Saudi_Arabia_Persian_Gulf.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3e0eae7018574f74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0adcd79009c7417f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R93b65d84e6944dad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R998b1c901658481c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5ce0c812f5ff431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R641d5081aa844920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R40f73e2443dc4457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R285eea340f67462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1065b6a8fce34643"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R45b3c876defe413d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9be7f5b773cf4289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4fd0a591c8784d7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ684CommercialTable" displayName="EEZ684CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ684CommercialTable" displayName="EEZ684CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ684FunctionalTable" displayName="EEZ684FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ684FunctionalTable" displayName="EEZ684FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ684ValidationTable" displayName="EEZ684ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ684ValidationTable" displayName="EEZ684ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7461,7 +7415,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc194c9911afb4121"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R256530df85dd4bb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7471,20 +7425,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7492,498 +7436,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>7291.3700037499</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.004070226442357</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>10.094160978450068</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>7291.3700037499</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>10.268024021623336</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$102,A2,'Species'!$U$2:$U$102))</x:f>
-        <x:v>74867.96234904781</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.004070226442357</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>10.094160978450068</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>73600.26257129357</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1267.699777754242</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0172241203151453</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.017224120315145246</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>45.93422267460001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4273492916011543</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>267.5157101998154</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>45.93422267460001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>279.9078063287615</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$102,A3,'Species'!$U$2:$U$102))</x:f>
-        <x:v>12857.347504264146</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4273492916011543</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>267.5157101998154</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>12288.126201272084</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>569.2213029920622</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0463228724761253</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.04632287247612542</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>86.8605566841</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.628531360354252</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>425.1394049634533</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>86.8605566841</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>783.326279199414</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$102,A4,'Species'!$U$2:$U$102))</x:f>
-        <x:v>68040.15667654584</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.628531360354252</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>425.1394049634533</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>36927.84538347258</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>31112.31129307326</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.8425162900784318</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.8425162900784318</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>8596.094244572001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.369894364173135</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>234.36586850390376</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>8596.094244572001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>273.58543187259176</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$102,A5,'Species'!$U$2:$U$102))</x:f>
-        <x:v>2351766.156318731</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.369894364173135</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>234.36586850390376</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2014631.0933705254</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>337135.06294820574</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.167343323578001</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.16734332357800097</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>33918.3487259613</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.806415562312645</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>640.3472699731808</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>33918.3487259613</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1268.5250878059023</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$102,A6,'Species'!$U$2:$U$102))</x:f>
-        <x:v>43026276.29583128</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.806415562312645</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>640.3472699731808</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>21719522.008667637</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>21306754.28716364</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.9809955430262567</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.9809955430262567</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>62.472979642300004</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.84915729511817</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>706.5734184972</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>62.472979642300004</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>707.4742658101115</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$102,A7,'Species'!$U$2:$U$102))</x:f>
-        <x:v>44198.02540540624</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.84915729511817</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>706.5734184972</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>44141.7467895659</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>56.278615840339626</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0012749521696238</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0012749521696237586</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1037.6190276994</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.000071861350979</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1000.1654805659256</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1037.6190276994</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1004.6780087056676</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$102,A8,'Species'!$U$2:$U$102))</x:f>
-        <x:v>1042473.0185441441</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.000071861350979</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1000.1654805659256</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1037790.7334833188</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>4682.285060825292</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0045117815275815</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.004511781527581499</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>964.9425629484999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.465579329750156</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2921.3213302529975</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>964.9425629484999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2981.2955581011197</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$102,A9,'Species'!$U$2:$U$102))</x:f>
-        <x:v>2876778.9767410727</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.465579329750156</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2921.3213302529975</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2818907.2916104486</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>57871.6851306241</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.02052982916567</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.02052982916567003</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R239f84c196724450"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf89f62cc7f3242dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7993,20 +7613,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8014,1038 +7624,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1063.0805244016</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.793215353730878</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>621.1769810829302</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1063.0805244016</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>641.2991916708523</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$102,A2,'Species'!$U$2:$U$102))</x:f>
-        <x:v>681752.680979772</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.793215353730878</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>621.1769810829302</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>660361.1507958443</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>21391.530183927738</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0323936836050205</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.03239368360502039</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>19.0694547148</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.15</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1412.5375446227554</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>19.0694547148</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1412.5375446227554</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$102,A3,'Species'!$U$2:$U$102))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>26936.320740138417</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.15</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1412.5375446227554</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>26936.320740138417</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>623.9476994075</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.54</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>346.73685045253166</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>623.9476994075</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$102,A4,'Species'!$U$2:$U$102))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>216345.66013965948</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.54</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>216345.66013965948</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>6025.213623966699</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.4358654101944825</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2728.1321914007785</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>6025.213623966699</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2877.956493168641</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$102,A5,'Species'!$U$2:$U$102))</x:f>
-        <x:v>17340302.671823118</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.4358654101944825</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2728.1321914007785</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>16437579.247610096</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>902723.424213022</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0549182705442635</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.054918270544263466</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>23.845204294400002</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.7299999999999995</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>537.0317963702522</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>23.845204294400002</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$102,A6,'Species'!$U$2:$U$102))</x:f>
-        <x:v>12805.632897037296</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.7299999999999995</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>537.0317963702522</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>12805.632897037285</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1.0913936421275139e-11</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>8.522762216461937e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1609.3766297297</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.1378459162424726</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1373.5545638064432</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1609.3766297297</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1883.1885601403524</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$102,A7,'Species'!$U$2:$U$102))</x:f>
-        <x:v>3030759.6580642066</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.1378459162424726</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1373.5545638064432</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2210566.6146486616</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>820193.043415545</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3710329460240687</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.37103294602406867</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1013.773823405</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.006424282926092</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1014.9024079811473</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1013.773823405</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1015.6776214528054</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$102,A8,'Species'!$U$2:$U$102))</x:f>
-        <x:v>1029667.3856471068</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.006424282926092</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1014.9024079811473</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1028881.494521989</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>785.8911251177778</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.000763830557068</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.000763830557068088</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>18.6858838251</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>18.6858838251</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>31.622776601683796</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$102,A9,'Species'!$U$2:$U$102))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>590.899529806154</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>590.899529806154</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>812.0713389155001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.309911260015496</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>204.13207961870702</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>812.0713389155001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>204.1325520003582</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$102,A10,'Species'!$U$2:$U$102))</x:f>
-        <x:v>165770.19481916883</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.309911260015496</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>204.13207961870702</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>165769.8112115689</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0.3836075999424793</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0000023140980685</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.000002314098068513139</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>13172.4011518568</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.6928660328362137</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>493.0216977012839</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>13172.4011518568</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>940.7797641227758</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$102,A11,'Species'!$U$2:$U$102))</x:f>
-        <x:v>12392328.44857442</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.6928660328362137</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>493.0216977012839</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6494279.578690788</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5898048.869883632</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.9081914011273053</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.9081914011273052</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2308.6327616415</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.159338129374888</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1443.2385788650524</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2308.6327616415</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1510.4751059918362</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$102,A12,'Species'!$U$2:$U$102))</x:f>
-        <x:v>3487132.3153366707</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.159338129374888</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1443.2385788650524</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3331907.86603278</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>155224.44930389058</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0465872573747703</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.04658725737477023</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>15788.0285188926</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.43581323537718</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>272.7804461588861</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>15788.0285188926</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>590.799790431205</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$102,A13,'Species'!$U$2:$U$102))</x:f>
-        <x:v>9327563.940283636</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.43581323537718</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>272.7804461588861</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4306665.463352741</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>5020898.476930895</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.165843625342128</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.165843625342128</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>7272.6841199248</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.0027960220384124</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>10.064588476406247</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>7272.6841199248</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>10.213156737516835</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$102,A14,'Species'!$U$2:$U$102))</x:f>
-        <x:v>74277.06281924166</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.0027960220384124</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>10.064588476406247</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>73196.57278593785</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1080.4900333038095</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0147614839353707</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.014761483935370641</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>34.2742828975</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.27</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>186.20871366628674</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>34.2742828975</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$102,A15,'Species'!$U$2:$U$102))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>6382.170130177887</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.27</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>6382.170130177887</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>494.0752467898</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.1166290535149406</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>130.80641812086148</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>494.0752467898</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>171.8011524730243</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$102,A16,'Species'!$U$2:$U$102))</x:f>
-        <x:v>84882.69680688155</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.1166290535149406</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>130.80641812086148</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>64628.21331475441</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>20254.48349212714</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.313400022270198</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.31340002227019803</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1098.9676717813</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.9746259508498363</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>943.2481255902261</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1098.9676717813</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>1291.53425046518</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$102,A17,'Species'!$U$2:$U$102))</x:f>
-        <x:v>1419354.3882595252</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.9746259508498363</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>943.2481255902261</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1036599.196491966</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>382755.19176755915</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.3692412583984919</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.3692412583984919</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>579.5801648129</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>579.5801648129</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$102,A18,'Species'!$U$2:$U$102))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>187548.46501568286</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>187548.46501568286</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>45.93422267460001</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.4273492916011543</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>267.5157101998154</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>45.93422267460001</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>279.9078063287615</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$102,A19,'Species'!$U$2:$U$102))</x:f>
-        <x:v>12857.347504264146</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.4273492916011543</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>267.5157101998154</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>12288.126201272084</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>569.2213029920622</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0463228724761253</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.04632287247612542</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc445c3ee290c4beb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf309bc169314d3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9220,7 +8156,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9319,7 +8255,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>49497257.9393705</x:v>
+        <x:v>27757809.108077534</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9333,7 +8269,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>49497257.93937052</x:v>
+        <x:v>36273332.4841109</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9347,7 +8283,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-21739448.83129298</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9361,7 +8297,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>7.450580596923828e-9</x:v>
+        <x:v>-13223925.455259614</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9372,9 +8308,9 @@
         <x:v>EEZ_684</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9386,47 +8322,19 @@
         <x:v>EEZ_684</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_684</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_684</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5edc37b6c72c4e0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R250c750a7dbd4d39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9473,7 +8381,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
